--- a/fhir/ValueSet-ehealth-device-types.xlsx
+++ b/fhir/ValueSet-ehealth-device-types.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -109,6 +109,9 @@
   </si>
   <si>
     <t>19892000</t>
+  </si>
+  <si>
+    <t>1187059002</t>
   </si>
   <si>
     <t/>
@@ -381,7 +384,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -418,16 +421,22 @@
       <c r="A5" t="s" s="2">
         <v>32</v>
       </c>
-      <c r="B5" t="s" s="2">
-        <v>32</v>
-      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
         <v>33</v>
       </c>
       <c r="B6" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
         <v>34</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/ValueSet-ehealth-device-types.xlsx
+++ b/fhir/ValueSet-ehealth-device-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-device-types.xlsx
+++ b/fhir/ValueSet-ehealth-device-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-device-types.xlsx
+++ b/fhir/ValueSet-ehealth-device-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-device-types.xlsx
+++ b/fhir/ValueSet-ehealth-device-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-device-types.xlsx
+++ b/fhir/ValueSet-ehealth-device-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-ehealth-device-types.xlsx
+++ b/fhir/ValueSet-ehealth-device-types.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
